--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,105 +785,105 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>PRUEBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>2026-03-04, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -893,39 +893,56 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-02, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>ZURI - ZENTRAL</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,510 +441,583 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BURDEOS CIUDAD LA SALLE</t>
+          <t>ARAGON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BURGOS CASTILLA RESERVADO</t>
+          <t>BAVIERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-03</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHAMONIX CIUDAD LA SALLE</t>
+          <t>BURDEOS CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EL CAMPO</t>
+          <t>BURGOS CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EL CASTELL IBERIA RESERVADO</t>
+          <t>CHAMONIX CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02, 2026-03-04, 2026-03-04, 2026-03-07</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02, 2026-03-04, 2026-03-04, 2026-03-09</t>
+          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GALLET CIUDAD LA SALLE</t>
+          <t>EL CAMPO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IZOLA ZENTRAL-CITIZZEN</t>
+          <t>EL CASTELL IBERIA RESERVADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LA ALMERIA ALSACIA RESERVADO</t>
+          <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LA CABRERA</t>
+          <t>IZOLA ZENTRAL-CITIZZEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LA PALMA</t>
+          <t>LA ALMERIA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-04, 2026-03-04</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04, 2026-03-04, 2026-03-04</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LA PEÑA</t>
+          <t>LA CABRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-26, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
+          <t>LA PALMA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LA TERRA ALSACIA RESERVADO</t>
+          <t>LA PEÑA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LOIRA CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>LA SCALA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LORCA</t>
+          <t>LA TERRA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>LOIRA CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>LORCA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-04</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-04, 2026-03-06</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-16, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>LYON 2 CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>LYON CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>MALAGA CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-25, 2026-02-25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PRUEBA</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-02, 2026-03-03, 2026-03-03</t>
+          <t>2026-02-03, 2026-02-24, 2026-02-24, 2026-02-27, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-19, 2026-02-19</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>SAN SEBASTIAN LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SAN SIMON LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>URBANISMO TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>ZURI - ZENTRAL</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-16, 2026-02-16, 2026-02-18</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-11</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-21, 2026-02-23, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25, 2026-02-25</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-02, 2026-02-04, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-13, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
         </is>
       </c>
     </row>
@@ -586,12 +586,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-04, 2026-02-11, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-27, 2026-02-27</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-04, 2026-02-10, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-16, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-20, 2026-02-25, 2026-02-25</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-02-25, 2026-02-25</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-24, 2026-02-24, 2026-02-27, 2026-02-27</t>
+          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-05, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-06, 2026-02-07, 2026-02-07, 2026-02-07, 2026-02-10, 2026-02-10, 2026-02-13, 2026-02-13, 2026-02-16, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-19, 2026-02-24</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19, 2026-02-19</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
     </row>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,583 +441,510 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
+          <t>2026-03-03, 2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARAGON</t>
+          <t>BURDEOS CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAVIERA</t>
+          <t>BURGOS CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-03</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BURDEOS CIUDAD LA SALLE</t>
+          <t>CHAMONIX CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BURGOS CASTILLA RESERVADO</t>
+          <t>EL CAMPO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHAMONIX CIUDAD LA SALLE</t>
+          <t>EL CASTELL IBERIA RESERVADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
+          <t>2026-03-02, 2026-03-04, 2026-03-07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
+          <t>2026-03-02, 2026-03-04, 2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EL CAMPO</t>
+          <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EL CASTELL IBERIA RESERVADO</t>
+          <t>IZOLA ZENTRAL-CITIZZEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GALLET CIUDAD LA SALLE</t>
+          <t>LA ALMERIA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IZOLA ZENTRAL-CITIZZEN</t>
+          <t>LA CABRERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-03-03, 2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LA ALMERIA ALSACIA RESERVADO</t>
+          <t>LA PALMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LA CABRERA</t>
+          <t>LA PEÑA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-02-26, 2026-02-28</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LA PALMA</t>
+          <t>LA SCALA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LA PEÑA</t>
+          <t>LA TERRA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
+          <t>LOIRA CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LA TERRA ALSACIA RESERVADO</t>
+          <t>LORCA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LOIRA CIUDAD LA SALLE</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LORCA</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
+          <t>2026-03-04, 2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LYON 2 CIUDAD LA SALLE</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LYON CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>PASEO SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MALAGA CASTILLA RESERVADO</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-02, 2026-03-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-02, 2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>PRUEBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
+          <t>2026-03-02, 2026-03-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
+          <t>2026-03-02, 2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
-        </is>
-      </c>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PROVENZA PRESTIGE</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>2026-03-04, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+          <t>2026-03-02, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>ZURI - ZENTRAL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>SAN SIMON LA QUINTA</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ZURI - ZENTRAL</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,105 +802,101 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>PRUEBA BARRANQUILLA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-03-02, 2026-03-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
+          <t>2026-03-02, 2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>2026-03-04, 2026-03-05</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -910,39 +906,56 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-02, 2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>ZURI - ZENTRAL</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,437 +441,429 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BURDEOS CIUDAD LA SALLE</t>
+          <t>ARAGON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BURGOS CASTILLA RESERVADO</t>
+          <t>BAVIERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-03</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHAMONIX CIUDAD LA SALLE</t>
+          <t>BURDEOS CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EL CAMPO</t>
+          <t>BURGOS CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EL CASTELL IBERIA RESERVADO</t>
+          <t>CHAMONIX CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-04, 2026-03-07</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-04, 2026-03-09</t>
+          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GALLET CIUDAD LA SALLE</t>
+          <t>EL CAMPO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IZOLA ZENTRAL-CITIZZEN</t>
+          <t>EL CASTELL IBERIA RESERVADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LA ALMERIA ALSACIA RESERVADO</t>
+          <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LA CABRERA</t>
+          <t>IZOLA ZENTRAL-CITIZZEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LA PALMA</t>
+          <t>LA ALMERIA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-04</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LA PEÑA</t>
+          <t>LA CABRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-26, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
+          <t>LA PALMA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LA TERRA ALSACIA RESERVADO</t>
+          <t>LA PEÑA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LOIRA CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>LA SCALA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LORCA</t>
+          <t>LA TERRA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>LOIRA CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>LORCA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-06</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>LYON 2 CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>LYON CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>MALAGA CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PRUEBA</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PRUEBA BARRANQUILLA</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-09</t>
+          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -879,85 +871,153 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>SAN LUCAS LA QUINTA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-05</t>
+          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>SAN SEBASTIAN LA QUINTA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>SAN SIMON LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>URBANISMO TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>ZURI - ZENTRAL</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,588 +436,544 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABADIA SAN RAFAEL</t>
+          <t>AMARETTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
+          <t>2025-11-07, 2025-11-13, 2025-11-20, 2025-11-27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
+          <t>2025-11-08, 2025-11-14, 2025-11-25, 2025-11-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARAGON</t>
+          <t>BURDEOS CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
+          <t>2025-11-04, 2025-11-10, 2025-11-18, 2025-11-25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
+          <t>2025-11-06, 2025-11-12, 2025-11-21, 2025-11-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAVIERA</t>
+          <t>CADIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-11-27, 2025-11-28</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BURDEOS CIUDAD LA SALLE</t>
+          <t>CHAMONIX CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
+          <t>2025-11-06, 2025-11-10, 2025-11-19, 2025-11-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
+          <t>2025-11-06, 2025-11-10, 2025-11-19, 2025-11-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BURGOS CASTILLA RESERVADO</t>
+          <t>EL CAMPO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
+          <t>2025-11-05, 2025-11-18, 2025-11-19, 2025-11-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHAMONIX CIUDAD LA SALLE</t>
+          <t>EL CASTELL IBERIA RESERVADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
+          <t>2025-11-01, 2025-11-08, 2025-11-15, 2025-11-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-11, 2025-11-15, 2025-11-25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EL CAMPO</t>
+          <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-10, 2025-11-14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
+          <t>2025-11-10, 2025-11-14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EL CASTELL IBERIA RESERVADO</t>
+          <t>IZOLA ZENTRAL-CITIZZEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
+          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GALLET CIUDAD LA SALLE</t>
+          <t>LA ALMERIA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IZOLA ZENTRAL-CITIZZEN</t>
+          <t>LA CABRERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LA ALMERIA ALSACIA RESERVADO</t>
+          <t>LA CRUZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2025-11-13, 2025-11-21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
+          <t>2025-11-21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LA CABRERA</t>
+          <t>LA PALMA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-28</t>
+          <t>2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-02-26, 2026-02-28</t>
+          <t>2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LA PALMA</t>
+          <t>LA PEÑA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2025-11-07, 2025-11-14, 2025-11-19, 2025-11-26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-28</t>
+          <t>2025-11-07, 2025-11-18, 2025-11-21, 2025-11-28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LA PEÑA</t>
+          <t>LA SCALA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-12, 2025-11-20, 2025-11-26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-12, 2025-11-20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
+          <t>LA TERRA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LA TERRA ALSACIA RESERVADO</t>
+          <t>LOIRA CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LOIRA CIUDAD LA SALLE</t>
+          <t>LORCA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>2025-11-04, 2025-11-17, 2025-11-19, 2025-11-27</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-17, 2025-11-20</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LORCA</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
+          <t>2025-11-06, 2025-11-14, 2025-11-20, 2025-11-27</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LYON 2 CIUDAD LA SALLE</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>2025-11-05, 2025-11-11, 2025-11-18, 2025-11-21, 2025-11-25, 2025-11-28</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-11-11, 2025-11-14, 2025-11-18, 2025-11-21, 2025-11-28</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LYON CIUDAD LA SALLE</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025-11-04, 2025-11-11, 2025-11-25</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MALAGA CASTILLA RESERVADO</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-19, 2025-11-26, 2025-11-28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-20, 2025-11-28</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2025-11-04, 2025-11-12, 2025-11-18, 2025-11-24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
+          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
+          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
+          <t>2025-11-06, 2025-11-13, 2025-11-24, 2025-11-27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
+          <t>2025-11-08, 2025-11-18, 2025-11-24, 2025-11-28</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
+          <t>2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
+          <t>2025-11-01, 2025-11-12, 2025-11-18, 2025-11-25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
+          <t>2025-11-06, 2025-11-12, 2025-11-20, 2025-11-26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
+          <t>2025-11-01, 2025-11-06, 2025-11-20, 2025-11-21, 2025-11-27</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PROVENZA PRESTIGE</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025-11-01, 2025-11-07, 2025-11-15, 2025-11-22, 2025-11-29</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAN LUCAS LA QUINTA</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+          <t>2025-11-01, 2025-11-12, 2025-11-19, 2025-11-27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+          <t>2025-11-01, 2025-11-12, 2025-11-13, 2025-11-21, 2025-11-27</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
+          <t>2025-11-06, 2025-11-14, 2025-11-21, 2025-11-26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+          <t>2025-11-06, 2025-11-20, 2025-11-22, 2025-11-27</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAN SEBASTIAN LA QUINTA</t>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+          <t>2025-11-07, 2025-11-14, 2025-11-24, 2025-11-29</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>ZURI - ZENTRAL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+          <t>2025-11-05, 2025-11-11, 2025-11-18, 2025-11-27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ZURI - ZENTRAL</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
+          <t>2025-11-05, 2025-11-13, 2025-11-19, 2025-11-27</t>
         </is>
       </c>
     </row>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,219 +759,236 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>PARQUE ORIENTE SOLEIL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25</t>
+          <t>2025-11-08, 2025-11-13, 2025-11-21, 2025-11-29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-25</t>
+          <t>2025-11-08, 2025-11-13, 2025-11-21, 2025-11-29</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-19, 2025-11-26, 2025-11-28</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-20, 2025-11-28</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PEÑAZUL EL POBLADO</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-24</t>
+          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-19, 2025-11-26, 2025-11-28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-12, 2025-11-18, 2025-11-24</t>
+          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-20, 2025-11-28</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>PEÑAZUL EL POBLADO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-25</t>
+          <t>2025-11-04, 2025-11-12, 2025-11-18, 2025-11-24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PUERTA DORADA CRISTALINA</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-24, 2025-11-27</t>
+          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-11-08, 2025-11-18, 2025-11-24, 2025-11-28</t>
+          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RIVERBAY</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25</t>
+          <t>2025-11-06, 2025-11-13, 2025-11-24, 2025-11-27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-12, 2025-11-18, 2025-11-25</t>
+          <t>2025-11-08, 2025-11-18, 2025-11-24, 2025-11-28</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-12, 2025-11-20, 2025-11-26</t>
+          <t>2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-06, 2025-11-20, 2025-11-21, 2025-11-27</t>
+          <t>2025-11-01, 2025-11-12, 2025-11-18, 2025-11-25</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
+          <t>2025-11-06, 2025-11-12, 2025-11-20, 2025-11-26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-07, 2025-11-15, 2025-11-22, 2025-11-29</t>
+          <t>2025-11-01, 2025-11-06, 2025-11-20, 2025-11-21, 2025-11-27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>SAN MATEO - LA QUINTA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
+          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
+          <t>2025-11-01, 2025-11-07, 2025-11-15, 2025-11-22, 2025-11-29</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>SAN SIMON LA QUINTA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-12, 2025-11-19, 2025-11-27</t>
+          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-12, 2025-11-13, 2025-11-21, 2025-11-27</t>
+          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-14, 2025-11-21, 2025-11-26</t>
+          <t>2025-11-01, 2025-11-12, 2025-11-19, 2025-11-27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-20, 2025-11-22, 2025-11-27</t>
+          <t>2025-11-01, 2025-11-12, 2025-11-13, 2025-11-21, 2025-11-27</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>URBANISMO TRES QUEBRADAS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-29</t>
+          <t>2025-11-06, 2025-11-14, 2025-11-21, 2025-11-26</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-14, 2025-11-24, 2025-11-29</t>
+          <t>2025-11-06, 2025-11-20, 2025-11-22, 2025-11-27</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-29</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2025-11-07, 2025-11-14, 2025-11-24, 2025-11-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>ZURI - ZENTRAL</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2025-11-05, 2025-11-11, 2025-11-18, 2025-11-27</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>2025-11-05, 2025-11-13, 2025-11-19, 2025-11-27</t>
         </is>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,561 +436,656 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMARETTO</t>
+          <t>ABADIA SAN RAFAEL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-13, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-11-08, 2025-11-14, 2025-11-25, 2025-11-28</t>
+          <t>2026-02-02, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16, 2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BURDEOS CIUDAD LA SALLE</t>
+          <t>AMARETTO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-10, 2025-11-18, 2025-11-25</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-12, 2025-11-21, 2025-11-26</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-21, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CADIZ</t>
+          <t>ARAGON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-06, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-11-27, 2025-11-28</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHAMONIX CIUDAD LA SALLE</t>
+          <t>BAVIERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-10, 2025-11-19, 2025-11-24</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2025-11-06, 2025-11-10, 2025-11-19, 2025-11-28</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EL CAMPO</t>
+          <t>BURDEOS CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-18, 2025-11-19, 2025-11-26</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EL CASTELL IBERIA RESERVADO</t>
+          <t>BURGOS CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-15, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-11, 2025-11-15, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-21, 2026-02-23, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GALLET CIUDAD LA SALLE</t>
+          <t>CHAMONIX CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-11-10, 2025-11-14</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-11-10, 2025-11-14</t>
+          <t>2026-02-04, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IZOLA ZENTRAL-CITIZZEN</t>
+          <t>EL CAMPO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25</t>
+          <t>2026-02-06, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-05, 2025-11-11, 2025-11-18, 2025-11-25</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-25, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LA ALMERIA ALSACIA RESERVADO</t>
+          <t>EL CASTELL IBERIA RESERVADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-06, 2026-02-13, 2026-02-17, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-02, 2026-02-04, 2026-02-09, 2026-02-13, 2026-02-17, 2026-02-26, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LA CABRERA</t>
+          <t>GALLET CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-15, 2025-11-22, 2025-11-29</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LA CRUZ</t>
+          <t>IZOLA ZENTRAL-CITIZZEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-11-13, 2025-11-21</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LA PALMA</t>
+          <t>LA ALMERIA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-15, 2025-11-19, 2025-11-29</t>
+          <t>2026-02-12, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LA PEÑA</t>
+          <t>LA CABRERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-14, 2025-11-19, 2025-11-26</t>
+          <t>2026-02-06, 2026-02-28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-18, 2025-11-21, 2025-11-28</t>
+          <t>2026-02-26, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LA SCALA</t>
+          <t>LA PALMA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-12, 2025-11-20, 2025-11-26</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-12, 2025-11-20</t>
+          <t>2026-02-05, 2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LA TERRA ALSACIA RESERVADO</t>
+          <t>LA PEÑA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-06, 2026-02-11, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-27</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LOIRA CIUDAD LA SALLE</t>
+          <t>LA SCALA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LORCA</t>
+          <t>LA TERRA ALSACIA RESERVADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-17, 2025-11-19, 2025-11-27</t>
+          <t>2026-02-03, 2026-02-12, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-17, 2025-11-20</t>
+          <t>2026-02-05, 2026-02-20, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>METROPOLI 30</t>
+          <t>LOIRA CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-26</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2025-11-06, 2025-11-14, 2025-11-20, 2025-11-27</t>
-        </is>
-      </c>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MONTPELLIER CIUDAD LA SALLE</t>
+          <t>LORCA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-11, 2025-11-18, 2025-11-21, 2025-11-25, 2025-11-28</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-12, 2026-02-16, 2026-02-19, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025-11-11, 2025-11-14, 2025-11-18, 2025-11-21, 2025-11-28</t>
+          <t>2026-02-03, 2026-02-04, 2026-02-06, 2026-02-10, 2026-02-14, 2026-02-16, 2026-02-20, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PARQUE ORIENTE SOLEIL</t>
+          <t>LYON 2 CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-11-08, 2025-11-13, 2025-11-21, 2025-11-29</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2025-11-08, 2025-11-13, 2025-11-21, 2025-11-29</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PASEO DE SEVILLA</t>
+          <t>LYON CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-25</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-25</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PASEO SAN RAFAEL</t>
+          <t>MALAGA CASTILLA RESERVADO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-19, 2025-11-26, 2025-11-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-11-05, 2025-11-07, 2025-11-12, 2025-11-14, 2025-11-20, 2025-11-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PEÑAZUL EL POBLADO</t>
+          <t>METROPOLI 30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-18, 2025-11-24</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-12, 2025-11-18, 2025-11-24</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PEÑON DE ALICANTE</t>
+          <t>MONTPELLIER CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-24</t>
+          <t>2026-02-05, 2026-02-09, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-08, 2025-11-14, 2025-11-15, 2025-11-25</t>
+          <t>2026-02-09, 2026-02-12, 2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PUERTA DORADA CRISTALINA</t>
+          <t>PARQUE ORIENTE SOLEIL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-24, 2025-11-27</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-11-08, 2025-11-18, 2025-11-24, 2025-11-28</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RIVERBAY</t>
+          <t>PASEO DE SEVILLA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-12, 2025-11-19, 2025-11-25</t>
+          <t>2026-02-03, 2026-02-10, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-12, 2025-11-18, 2025-11-25</t>
+          <t>2026-02-03, 2026-02-24, 2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SAINT MICHEL CIUDAD LA SALLE</t>
+          <t>PASEO SAN RAFAEL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-12, 2025-11-20, 2025-11-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-06, 2025-11-20, 2025-11-21, 2025-11-27</t>
+          <t>2026-02-06, 2026-02-13, 2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAN MATEO - LA QUINTA</t>
+          <t>PEÑON DE ALICANTE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-11, 2025-11-19, 2025-11-25</t>
+          <t>2026-02-02, 2026-02-10, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-07, 2025-11-15, 2025-11-22, 2025-11-29</t>
+          <t>2026-02-02, 2026-02-11, 2026-02-17, 2026-02-24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAN SIMON LA QUINTA</t>
+          <t>PROVENZA PRESTIGE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2025-11-04, 2025-11-06, 2025-11-12</t>
-        </is>
-      </c>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>URB EXTERNO CIUDAD LA SALLE</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-12, 2025-11-19, 2025-11-27</t>
+          <t>2026-02-03, 2026-02-05, 2026-02-12, 2026-02-20, 2026-02-26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2025-11-01, 2025-11-12, 2025-11-13, 2025-11-21, 2025-11-27</t>
+          <t>2026-02-02, 2026-02-03, 2026-02-10, 2026-02-18, 2026-02-23</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>URBANISMO TRES QUEBRADAS</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-14, 2025-11-21, 2025-11-26</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-19, 2026-02-25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-20, 2025-11-22, 2025-11-27</t>
+          <t>2026-02-03, 2026-02-05, 2026-02-18, 2026-02-24, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+          <t>SAINT MICHEL CIUDAD LA SALLE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-11-06, 2025-11-13, 2025-11-20, 2025-11-29</t>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2025-11-07, 2025-11-14, 2025-11-24, 2025-11-29</t>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>SAN LUCAS LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-10, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SAN MATEO - LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-11, 2026-02-19, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-02-07, 2026-02-13, 2026-02-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SAN SEBASTIAN LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-12, 2026-02-20, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SAN SIMON LA QUINTA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-06, 2026-02-13, 2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>URB EXTERNO CIUDAD LA SALLE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-11, 2026-02-18, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>URBANISMO TRES QUEBRADAS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-16, 2026-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>VERDANIA BOSQUES DE GUAYMARAL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-14, 2026-02-20, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-02-10, 2026-02-14, 2026-02-21, 2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>ZURI - ZENTRAL</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2025-11-05, 2025-11-11, 2025-11-18, 2025-11-27</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2025-11-05, 2025-11-13, 2025-11-19, 2025-11-27</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-13, 2026-02-19, 2026-02-27</t>
         </is>
       </c>
     </row>
